--- a/363/BIOL 363 Mussel MR Lab 09262026 Class data.xlsx
+++ b/363/BIOL 363 Mussel MR Lab 09262026 Class data.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hello\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hello\Documents\code2026\2026-BIOL-Coursework\363\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E884C2C-B569-4282-91A8-A3D592E3FFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{808A42E7-8693-437F-92AB-BABCBEBE67C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Standardized" sheetId="2" r:id="rId1"/>
-    <sheet name="Raw" sheetId="1" r:id="rId2"/>
+    <sheet name="Sample" sheetId="3" r:id="rId1"/>
+    <sheet name="Standardized" sheetId="2" r:id="rId2"/>
+    <sheet name="Raw" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="56">
   <si>
     <t>DO2 (mg/L)</t>
   </si>
@@ -186,10 +187,25 @@
     <t>Change in DO2</t>
   </si>
   <si>
-    <t>Change in DO2 per minute per gram</t>
-  </si>
-  <si>
-    <t>s</t>
+    <t>Change in DO2 per minute per L</t>
+  </si>
+  <si>
+    <t>Sample size</t>
+  </si>
+  <si>
+    <t>Confidence Interval</t>
+  </si>
+  <si>
+    <t>Standard deviation</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>a.</t>
+  </si>
+  <si>
+    <t>b.</t>
   </si>
 </sst>
 </file>
@@ -317,7 +333,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -348,6 +364,13 @@
     <xf numFmtId="21" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -360,13 +383,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -680,8 +713,1177 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A555839-2B72-498C-BC8A-0CD764DC361A}">
+  <dimension ref="A1:R25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="14" max="14" width="19.5546875" customWidth="1"/>
+    <col min="15" max="15" width="20.44140625" customWidth="1"/>
+    <col min="16" max="16" width="17.88671875" customWidth="1"/>
+    <col min="17" max="17" width="23.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="19"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row r="2" spans="1:18" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="7">
+        <v>7.69</v>
+      </c>
+      <c r="D3" s="7">
+        <v>7.25</v>
+      </c>
+      <c r="E3" s="7">
+        <f>D3-C3</f>
+        <v>-0.44000000000000039</v>
+      </c>
+      <c r="F3" s="9">
+        <v>0.65555555555555556</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="15">
+        <v>53.67</v>
+      </c>
+      <c r="I3" s="7">
+        <v>1.409</v>
+      </c>
+      <c r="J3" s="7">
+        <v>25.89</v>
+      </c>
+      <c r="K3" s="7">
+        <v>68</v>
+      </c>
+      <c r="L3" s="7">
+        <f>E3 / H3 / I3</f>
+        <v>-5.8184872647198847E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
+        <v>4</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="7">
+        <v>7.45</v>
+      </c>
+      <c r="D4" s="7">
+        <v>6.87</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" ref="E4:E25" si="0">D4-C4</f>
+        <v>-0.58000000000000007</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0.69097222222222221</v>
+      </c>
+      <c r="H4" s="16">
+        <v>60</v>
+      </c>
+      <c r="I4" s="7">
+        <v>1.448</v>
+      </c>
+      <c r="J4" s="7">
+        <v>24.73</v>
+      </c>
+      <c r="K4" s="7">
+        <v>74</v>
+      </c>
+      <c r="L4" s="7">
+        <f t="shared" ref="L4:L25" si="1">E4 / H4 / I4</f>
+        <v>-6.675874769797422E-3</v>
+      </c>
+      <c r="O4" s="1"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
+        <v>7</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="7">
+        <v>7.48</v>
+      </c>
+      <c r="D5" s="7">
+        <v>6.36</v>
+      </c>
+      <c r="E5" s="7">
+        <f t="shared" si="0"/>
+        <v>-1.1200000000000001</v>
+      </c>
+      <c r="F5" s="9">
+        <v>0.64166666666666672</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0.19097222222222221</v>
+      </c>
+      <c r="H5" s="16">
+        <v>66.78</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1.345</v>
+      </c>
+      <c r="J5" s="7">
+        <v>28.43</v>
+      </c>
+      <c r="K5" s="7">
+        <v>74</v>
+      </c>
+      <c r="L5" s="7">
+        <f t="shared" si="1"/>
+        <v>-1.2469508155837679E-2</v>
+      </c>
+      <c r="O5" s="24"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+    </row>
+    <row r="6" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
+        <v>10</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="7">
+        <v>7.65</v>
+      </c>
+      <c r="D6" s="7">
+        <v>7.38</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" si="0"/>
+        <v>-0.27000000000000046</v>
+      </c>
+      <c r="F6" s="9">
+        <v>0.65</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0.69166666666666676</v>
+      </c>
+      <c r="H6" s="16">
+        <v>60</v>
+      </c>
+      <c r="I6" s="7">
+        <v>1.35</v>
+      </c>
+      <c r="J6" s="7">
+        <v>33.96</v>
+      </c>
+      <c r="K6" s="7">
+        <v>77</v>
+      </c>
+      <c r="L6" s="7">
+        <f t="shared" si="1"/>
+        <v>-3.3333333333333388E-3</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O6" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="P6" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q6" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="R6" s="22"/>
+    </row>
+    <row r="7" spans="1:18" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="6">
+        <v>11</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="7">
+        <v>8.1</v>
+      </c>
+      <c r="D7" s="7">
+        <v>7.92</v>
+      </c>
+      <c r="E7" s="7">
+        <f t="shared" si="0"/>
+        <v>-0.17999999999999972</v>
+      </c>
+      <c r="F7" s="11">
+        <v>0.64027777777777783</v>
+      </c>
+      <c r="G7" s="11">
+        <v>0.69861111111111107</v>
+      </c>
+      <c r="H7" s="16">
+        <v>60</v>
+      </c>
+      <c r="I7" s="7">
+        <v>1.375</v>
+      </c>
+      <c r="J7" s="7">
+        <v>14.68</v>
+      </c>
+      <c r="K7" s="7">
+        <v>59</v>
+      </c>
+      <c r="L7" s="7">
+        <f t="shared" si="1"/>
+        <v>-2.1818181818181784E-3</v>
+      </c>
+      <c r="N7" s="1"/>
+      <c r="O7" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="P7" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q7" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="6">
+        <v>12</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="7">
+        <v>7.69</v>
+      </c>
+      <c r="D8" s="7">
+        <v>6.3</v>
+      </c>
+      <c r="E8" s="7">
+        <f t="shared" si="0"/>
+        <v>-1.3900000000000006</v>
+      </c>
+      <c r="F8" s="10">
+        <v>0.64444444444444449</v>
+      </c>
+      <c r="G8" s="8">
+        <v>0.68611111111111101</v>
+      </c>
+      <c r="H8" s="16">
+        <v>60</v>
+      </c>
+      <c r="I8" s="7">
+        <v>1.476</v>
+      </c>
+      <c r="J8" s="7">
+        <v>28.65</v>
+      </c>
+      <c r="K8" s="7">
+        <v>79</v>
+      </c>
+      <c r="L8" s="7">
+        <f t="shared" si="1"/>
+        <v>-1.5695573622402897E-2</v>
+      </c>
+      <c r="N8" s="1"/>
+      <c r="O8" s="7">
+        <v>-5.8184872647198847E-3</v>
+      </c>
+      <c r="P8" s="7">
+        <v>-1.1172925386847688E-2</v>
+      </c>
+      <c r="Q8" s="7">
+        <v>-6.2256125361863706E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <v>21</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="7">
+        <v>7.18</v>
+      </c>
+      <c r="D9" s="7">
+        <v>6.96</v>
+      </c>
+      <c r="E9" s="7">
+        <f t="shared" si="0"/>
+        <v>-0.21999999999999975</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="16">
+        <v>60</v>
+      </c>
+      <c r="I9" s="7">
+        <v>1.395</v>
+      </c>
+      <c r="J9" s="7">
+        <v>24.05</v>
+      </c>
+      <c r="K9" s="7">
+        <v>55</v>
+      </c>
+      <c r="L9" s="7">
+        <f t="shared" si="1"/>
+        <v>-2.6284348864993997E-3</v>
+      </c>
+      <c r="N9" s="21"/>
+      <c r="O9" s="7">
+        <v>-6.675874769797422E-3</v>
+      </c>
+      <c r="P9" s="7">
+        <v>-1.0745585930183264E-2</v>
+      </c>
+      <c r="Q9" s="7">
+        <v>-1.0014204545454547E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
+        <v>22</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="7">
+        <v>7.51</v>
+      </c>
+      <c r="D10" s="7">
+        <v>6.27</v>
+      </c>
+      <c r="E10" s="7">
+        <f t="shared" si="0"/>
+        <v>-1.2400000000000002</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0.6875</v>
+      </c>
+      <c r="H10" s="16">
+        <v>75</v>
+      </c>
+      <c r="I10" s="7">
+        <v>1.4179999999999999</v>
+      </c>
+      <c r="J10" s="7">
+        <v>27.63</v>
+      </c>
+      <c r="K10" s="7">
+        <v>70</v>
+      </c>
+      <c r="L10" s="7">
+        <f t="shared" si="1"/>
+        <v>-1.1659614480488955E-2</v>
+      </c>
+      <c r="O10" s="7">
+        <v>-1.2469508155837679E-2</v>
+      </c>
+      <c r="P10" s="7">
+        <v>-4.3117744610281887E-3</v>
+      </c>
+      <c r="Q10" s="7">
+        <v>-1.0521885521885521E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="6">
+        <v>3</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="7">
+        <v>7.49</v>
+      </c>
+      <c r="D11" s="7">
+        <v>6.55</v>
+      </c>
+      <c r="E11" s="7">
+        <f t="shared" si="0"/>
+        <v>-0.94000000000000039</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0.64930555555555558</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0.19236111111111112</v>
+      </c>
+      <c r="H11" s="16">
+        <v>62.09</v>
+      </c>
+      <c r="I11" s="7">
+        <v>1.355</v>
+      </c>
+      <c r="J11" s="7">
+        <v>26.59</v>
+      </c>
+      <c r="K11" s="7">
+        <v>75</v>
+      </c>
+      <c r="L11" s="7">
+        <f t="shared" si="1"/>
+        <v>-1.1172925386847688E-2</v>
+      </c>
+      <c r="O11" s="7">
+        <v>-3.3333333333333388E-3</v>
+      </c>
+      <c r="P11" s="7">
+        <v>-1.0673038630027876E-2</v>
+      </c>
+      <c r="Q11" s="7">
+        <v>-1.4490084116166275E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="6">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="7">
+        <v>7.66</v>
+      </c>
+      <c r="D12" s="7">
+        <v>6.57</v>
+      </c>
+      <c r="E12" s="7">
+        <f t="shared" si="0"/>
+        <v>-1.0899999999999999</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0.69166666666666676</v>
+      </c>
+      <c r="H12" s="16">
+        <v>75.25</v>
+      </c>
+      <c r="I12" s="7">
+        <v>1.3480000000000001</v>
+      </c>
+      <c r="J12" s="7">
+        <v>33.42</v>
+      </c>
+      <c r="K12" s="7">
+        <v>80</v>
+      </c>
+      <c r="L12" s="7">
+        <f t="shared" si="1"/>
+        <v>-1.0745585930183264E-2</v>
+      </c>
+      <c r="O12" s="7">
+        <v>-2.1818181818181784E-3</v>
+      </c>
+      <c r="P12" s="7">
+        <v>-5.0793650793650776E-3</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>-6.635267632335076E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" s="6">
+        <v>15</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="7">
+        <v>7.72</v>
+      </c>
+      <c r="D13" s="7">
+        <v>7.33</v>
+      </c>
+      <c r="E13" s="7">
+        <f t="shared" si="0"/>
+        <v>-0.38999999999999968</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0.64166666666666672</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0.68819444444444444</v>
+      </c>
+      <c r="H13" s="16">
+        <v>67</v>
+      </c>
+      <c r="I13" s="7">
+        <v>1.35</v>
+      </c>
+      <c r="J13" s="7">
+        <v>27.54</v>
+      </c>
+      <c r="K13" s="7">
+        <v>80</v>
+      </c>
+      <c r="L13" s="7">
+        <f t="shared" si="1"/>
+        <v>-4.3117744610281887E-3</v>
+      </c>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7">
+        <v>-8.2185158327290272E-3</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>-1.3493519559685158E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="6">
+        <v>16</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="7">
+        <v>7.04</v>
+      </c>
+      <c r="D14" s="7">
+        <v>6.37</v>
+      </c>
+      <c r="E14" s="7">
+        <f t="shared" si="0"/>
+        <v>-0.66999999999999993</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="16">
+        <v>45</v>
+      </c>
+      <c r="I14" s="7">
+        <v>1.395</v>
+      </c>
+      <c r="J14" s="7">
+        <v>21.92</v>
+      </c>
+      <c r="K14" s="7">
+        <v>66</v>
+      </c>
+      <c r="L14" s="7">
+        <f t="shared" si="1"/>
+        <v>-1.0673038630027876E-2</v>
+      </c>
+      <c r="O14" s="7">
+        <v>-2.6284348864993997E-3</v>
+      </c>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7">
+        <v>-6.5069818156237857E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" s="6">
+        <v>17</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="7">
+        <v>7.77</v>
+      </c>
+      <c r="D15" s="7">
+        <v>7.13</v>
+      </c>
+      <c r="E15" s="7">
+        <f t="shared" si="0"/>
+        <v>-0.63999999999999968</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="16">
+        <v>90</v>
+      </c>
+      <c r="I15" s="7">
+        <v>1.4</v>
+      </c>
+      <c r="J15" s="7">
+        <v>28.96</v>
+      </c>
+      <c r="K15" s="7">
+        <v>68</v>
+      </c>
+      <c r="L15" s="7">
+        <f t="shared" si="1"/>
+        <v>-5.0793650793650776E-3</v>
+      </c>
+      <c r="O15" s="7">
+        <v>-1.1659614480488955E-2</v>
+      </c>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7">
+        <v>-7.5433503934000468E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" s="6">
+        <v>18</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="7">
+        <v>7.34</v>
+      </c>
+      <c r="D16" s="7">
+        <v>6.66</v>
+      </c>
+      <c r="E16" s="7">
+        <f t="shared" si="0"/>
+        <v>-0.67999999999999972</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="16">
+        <v>60</v>
+      </c>
+      <c r="I16" s="7">
+        <v>1.379</v>
+      </c>
+      <c r="J16" s="7">
+        <v>28.75</v>
+      </c>
+      <c r="K16" s="7">
+        <v>75.5</v>
+      </c>
+      <c r="L16" s="7">
+        <f t="shared" si="1"/>
+        <v>-8.2185158327290272E-3</v>
+      </c>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7">
+        <v>-1.1574074074074075E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A17" s="6">
+        <v>1</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="7">
+        <v>7.64</v>
+      </c>
+      <c r="D17" s="7">
+        <v>6.96</v>
+      </c>
+      <c r="E17" s="7">
+        <f t="shared" si="0"/>
+        <v>-0.67999999999999972</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0.63888888888888895</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0.69305555555555554</v>
+      </c>
+      <c r="H17" s="16">
+        <v>78.58</v>
+      </c>
+      <c r="I17" s="7">
+        <v>1.39</v>
+      </c>
+      <c r="J17" s="7">
+        <v>15.33</v>
+      </c>
+      <c r="K17" s="7">
+        <v>60</v>
+      </c>
+      <c r="L17" s="7">
+        <f t="shared" si="1"/>
+        <v>-6.2256125361863706E-3</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="6">
+        <v>5</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="7">
+        <v>7.8</v>
+      </c>
+      <c r="D18" s="7">
+        <v>6.39</v>
+      </c>
+      <c r="E18" s="7">
+        <f t="shared" si="0"/>
+        <v>-1.4100000000000001</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="16">
+        <v>100</v>
+      </c>
+      <c r="I18" s="7">
+        <v>1.4079999999999999</v>
+      </c>
+      <c r="J18" s="7">
+        <v>17.63</v>
+      </c>
+      <c r="K18" s="7">
+        <v>60</v>
+      </c>
+      <c r="L18" s="7">
+        <f t="shared" si="1"/>
+        <v>-1.0014204545454547E-2</v>
+      </c>
+      <c r="N18" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="O18" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="P18" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q18" s="27" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A19" s="6">
+        <v>6</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="7">
+        <v>8.1</v>
+      </c>
+      <c r="D19" s="7">
+        <v>6.85</v>
+      </c>
+      <c r="E19" s="7">
+        <f t="shared" si="0"/>
+        <v>-1.25</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="16">
+        <v>80</v>
+      </c>
+      <c r="I19" s="7">
+        <v>1.4850000000000001</v>
+      </c>
+      <c r="J19" s="7">
+        <v>23.2</v>
+      </c>
+      <c r="K19" s="7">
+        <v>65</v>
+      </c>
+      <c r="L19" s="7">
+        <f t="shared" si="1"/>
+        <v>-1.0521885521885521E-2</v>
+      </c>
+      <c r="N19" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="O19" s="7">
+        <v>8</v>
+      </c>
+      <c r="P19" s="7">
+        <v>6</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A20" s="6">
+        <v>9</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="7">
+        <v>7.2</v>
+      </c>
+      <c r="D20" s="7">
+        <v>6.02</v>
+      </c>
+      <c r="E20" s="7">
+        <f t="shared" si="0"/>
+        <v>-1.1800000000000006</v>
+      </c>
+      <c r="F20" s="8">
+        <v>0.63472222222222219</v>
+      </c>
+      <c r="G20" s="8">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="H20" s="16">
+        <v>61</v>
+      </c>
+      <c r="I20" s="7">
+        <v>1.335</v>
+      </c>
+      <c r="J20" s="7">
+        <v>32.659999999999997</v>
+      </c>
+      <c r="K20" s="7">
+        <v>81</v>
+      </c>
+      <c r="L20" s="7">
+        <f t="shared" si="1"/>
+        <v>-1.4490084116166275E-2</v>
+      </c>
+      <c r="N20" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="O20" s="7">
+        <f>AVERAGE(O8:O15)</f>
+        <v>-6.3952958674992648E-3</v>
+      </c>
+      <c r="P20" s="7">
+        <f>AVERAGE(P8:P13)</f>
+        <v>-8.36686755336352E-3</v>
+      </c>
+      <c r="Q20" s="7">
+        <f>AVERAGE(Q8:Q16)</f>
+        <v>-9.6672200216456495E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A21" s="6">
+        <v>13</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="7">
+        <v>7.56</v>
+      </c>
+      <c r="D21" s="7">
+        <v>7</v>
+      </c>
+      <c r="E21" s="7">
+        <f t="shared" si="0"/>
+        <v>-0.55999999999999961</v>
+      </c>
+      <c r="F21" s="9">
+        <v>0.14444444444444446</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0.19444444444444445</v>
+      </c>
+      <c r="H21" s="16">
+        <v>60.5</v>
+      </c>
+      <c r="I21" s="7">
+        <v>1.395</v>
+      </c>
+      <c r="J21" s="7">
+        <v>16.02</v>
+      </c>
+      <c r="K21" s="7">
+        <v>65</v>
+      </c>
+      <c r="L21" s="7">
+        <f t="shared" si="1"/>
+        <v>-6.635267632335076E-3</v>
+      </c>
+      <c r="N21" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="O21" s="7">
+        <f>_xlfn.STDEV.S(O8:O15)</f>
+        <v>4.2098849645026675E-3</v>
+      </c>
+      <c r="P21" s="7">
+        <f>_xlfn.STDEV.S(P8:P13)</f>
+        <v>3.037240440037232E-3</v>
+      </c>
+      <c r="Q21" s="7">
+        <f>_xlfn.STDEV.S(Q8:Q16)</f>
+        <v>3.1209544829054977E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A22" s="6">
+        <v>14</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="7">
+        <v>7.53</v>
+      </c>
+      <c r="D22" s="7">
+        <v>6.39</v>
+      </c>
+      <c r="E22" s="7">
+        <f t="shared" si="0"/>
+        <v>-1.1400000000000006</v>
+      </c>
+      <c r="F22" s="10">
+        <v>0.63611111111111118</v>
+      </c>
+      <c r="G22" s="8">
+        <v>0.67847222222222225</v>
+      </c>
+      <c r="H22" s="16">
+        <v>61</v>
+      </c>
+      <c r="I22" s="7">
+        <v>1.385</v>
+      </c>
+      <c r="J22" s="7">
+        <v>35.479999999999997</v>
+      </c>
+      <c r="K22" s="7">
+        <v>68</v>
+      </c>
+      <c r="L22" s="7">
+        <f t="shared" si="1"/>
+        <v>-1.3493519559685158E-2</v>
+      </c>
+      <c r="N22" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="O22" s="7">
+        <f>_xlfn.CONFIDENCE.NORM(0.95, O21, O19)</f>
+        <v>9.3333966191274078E-5</v>
+      </c>
+      <c r="P22" s="7">
+        <f>_xlfn.CONFIDENCE.NORM(0.95, P21, P19)</f>
+        <v>7.7753157527886988E-5</v>
+      </c>
+      <c r="Q22" s="7">
+        <f>_xlfn.CONFIDENCE.NORM(0.95, Q21, Q19)</f>
+        <v>6.5234999910144287E-5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A23" s="6">
+        <v>19</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="7">
+        <v>7.56</v>
+      </c>
+      <c r="D23" s="7">
+        <v>6.82</v>
+      </c>
+      <c r="E23" s="7">
+        <f t="shared" si="0"/>
+        <v>-0.73999999999999932</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" s="16">
+        <v>78</v>
+      </c>
+      <c r="I23" s="7">
+        <v>1.458</v>
+      </c>
+      <c r="J23" s="7">
+        <v>22.6</v>
+      </c>
+      <c r="K23" s="7">
+        <v>68</v>
+      </c>
+      <c r="L23" s="7">
+        <f t="shared" si="1"/>
+        <v>-6.5069818156237857E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A24" s="6">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="7">
+        <v>7.88</v>
+      </c>
+      <c r="D24" s="7">
+        <v>7.09</v>
+      </c>
+      <c r="E24" s="7">
+        <f t="shared" si="0"/>
+        <v>-0.79</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24" s="16">
+        <v>76</v>
+      </c>
+      <c r="I24" s="7">
+        <v>1.3779999999999999</v>
+      </c>
+      <c r="J24" s="7">
+        <v>21.57</v>
+      </c>
+      <c r="K24" s="7">
+        <v>69</v>
+      </c>
+      <c r="L24" s="7">
+        <f t="shared" si="1"/>
+        <v>-7.5433503934000468E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A25" s="6">
+        <v>23</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="7">
+        <v>7.29</v>
+      </c>
+      <c r="D25" s="7">
+        <v>6.29</v>
+      </c>
+      <c r="E25" s="7">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" s="16">
+        <v>60</v>
+      </c>
+      <c r="I25" s="7">
+        <v>1.44</v>
+      </c>
+      <c r="J25" s="7">
+        <v>27.27</v>
+      </c>
+      <c r="K25" s="7">
+        <v>66</v>
+      </c>
+      <c r="L25" s="7">
+        <f t="shared" si="1"/>
+        <v>-1.1574074074074075E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="F1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50B0EA87-795C-42B8-ADAC-DF50183C9869}">
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" customWidth="1"/>
@@ -750,16 +1952,16 @@
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="15" t="s">
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="16"/>
-      <c r="I4" s="17"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="20"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
@@ -790,7 +1992,7 @@
       <c r="H5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="14" t="s">
         <v>12</v>
       </c>
       <c r="J5" s="4" t="s">
@@ -830,7 +2032,7 @@
       <c r="H6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="15">
         <v>53.67</v>
       </c>
       <c r="J6" s="7">
@@ -843,8 +2045,8 @@
         <v>68</v>
       </c>
       <c r="M6" s="7">
-        <f>F6 / I6 / K6</f>
-        <v>-3.1665695465393269E-4</v>
+        <f>F6 / I6 / J6</f>
+        <v>-5.8184872647198847E-3</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -862,7 +2064,7 @@
         <v>6.87</v>
       </c>
       <c r="F7" s="7">
-        <f t="shared" ref="F7:F28" si="0">E7-D7</f>
+        <f t="shared" ref="F7:F27" si="0">E7-D7</f>
         <v>-0.58000000000000007</v>
       </c>
       <c r="G7" s="10" t="s">
@@ -871,7 +2073,7 @@
       <c r="H7" s="8">
         <v>0.69097222222222221</v>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="16">
         <v>60</v>
       </c>
       <c r="J7" s="7">
@@ -884,8 +2086,8 @@
         <v>74</v>
       </c>
       <c r="M7" s="7">
-        <f t="shared" ref="M7:M28" si="1">F7 / I7 / K7</f>
-        <v>-3.9088825987329832E-4</v>
+        <f t="shared" ref="M7:M27" si="1">F7 / I7 / J7</f>
+        <v>-6.675874769797422E-3</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -912,7 +2114,7 @@
       <c r="H8" s="9">
         <v>0.19097222222222221</v>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="16">
         <v>66.78</v>
       </c>
       <c r="J8" s="7">
@@ -926,7 +2128,7 @@
       </c>
       <c r="M8" s="7">
         <f t="shared" si="1"/>
-        <v>-5.8992221138240159E-4</v>
+        <v>-1.2469508155837679E-2</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -953,7 +2155,7 @@
       <c r="H9" s="9">
         <v>0.69166666666666676</v>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="16">
         <v>60</v>
       </c>
       <c r="J9" s="7">
@@ -967,7 +2169,7 @@
       </c>
       <c r="M9" s="7">
         <f t="shared" si="1"/>
-        <v>-1.3250883392226169E-4</v>
+        <v>-3.3333333333333388E-3</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -994,7 +2196,7 @@
       <c r="H10" s="11">
         <v>0.69861111111111107</v>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="16">
         <v>60</v>
       </c>
       <c r="J10" s="7">
@@ -1008,747 +2210,704 @@
       </c>
       <c r="M10" s="7">
         <f t="shared" si="1"/>
-        <v>-2.0435967302452284E-4</v>
+        <v>-2.1818181818181784E-3</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>42</v>
-      </c>
+      <c r="C11" s="7"/>
       <c r="D11" s="7">
-        <v>7.69</v>
+        <v>7.18</v>
       </c>
       <c r="E11" s="7">
-        <v>6.3</v>
+        <v>6.96</v>
       </c>
       <c r="F11" s="7">
         <f t="shared" si="0"/>
-        <v>-1.3900000000000006</v>
-      </c>
-      <c r="G11" s="10">
-        <v>0.64444444444444449</v>
-      </c>
-      <c r="H11" s="8">
-        <v>0.68611111111111101</v>
-      </c>
-      <c r="I11" s="20">
+        <v>-0.21999999999999975</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" s="16">
         <v>60</v>
       </c>
       <c r="J11" s="7">
-        <v>1.476</v>
+        <v>1.395</v>
       </c>
       <c r="K11" s="7">
-        <v>28.65</v>
+        <v>24.05</v>
       </c>
       <c r="L11" s="7">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="M11" s="7">
         <f t="shared" si="1"/>
-        <v>-8.0860965677719639E-4</v>
+        <v>-2.6284348864993997E-3</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7">
-        <v>7.18</v>
+        <v>7.51</v>
       </c>
       <c r="E12" s="7">
-        <v>6.96</v>
+        <v>6.27</v>
       </c>
       <c r="F12" s="7">
         <f t="shared" si="0"/>
-        <v>-0.21999999999999975</v>
+        <v>-1.2400000000000002</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" s="20">
-        <v>60</v>
+        <v>47</v>
+      </c>
+      <c r="H12" s="12">
+        <v>0.6875</v>
+      </c>
+      <c r="I12" s="16">
+        <v>75</v>
       </c>
       <c r="J12" s="7">
-        <v>1.395</v>
+        <v>1.4179999999999999</v>
       </c>
       <c r="K12" s="7">
-        <v>24.05</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>50</v>
+        <v>27.63</v>
+      </c>
+      <c r="L12" s="7">
+        <v>70</v>
       </c>
       <c r="M12" s="7">
         <f t="shared" si="1"/>
-        <v>-1.5246015246015229E-4</v>
+        <v>-1.1659614480488955E-2</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="C13" s="6"/>
       <c r="D13" s="7">
-        <v>7.51</v>
+        <v>7.49</v>
       </c>
       <c r="E13" s="7">
-        <v>6.27</v>
+        <v>6.55</v>
       </c>
       <c r="F13" s="7">
         <f t="shared" si="0"/>
-        <v>-1.2400000000000002</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="12">
-        <v>0.6875</v>
-      </c>
-      <c r="I13" s="20">
+        <v>-0.94000000000000039</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0.64930555555555558</v>
+      </c>
+      <c r="H13" s="9">
+        <v>0.19236111111111112</v>
+      </c>
+      <c r="I13" s="16">
+        <v>62.09</v>
+      </c>
+      <c r="J13" s="7">
+        <v>1.355</v>
+      </c>
+      <c r="K13" s="7">
+        <v>26.59</v>
+      </c>
+      <c r="L13" s="7">
         <v>75</v>
       </c>
-      <c r="J13" s="7">
-        <v>1.4179999999999999</v>
-      </c>
-      <c r="K13" s="7">
-        <v>27.63</v>
-      </c>
-      <c r="L13" s="7">
-        <v>70</v>
-      </c>
       <c r="M13" s="7">
         <f t="shared" si="1"/>
-        <v>-5.9838339968633142E-4</v>
+        <v>-1.1172925386847688E-2</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="7">
-        <v>7.49</v>
+        <v>7.66</v>
       </c>
       <c r="E14" s="7">
-        <v>6.55</v>
+        <v>6.57</v>
       </c>
       <c r="F14" s="7">
         <f t="shared" si="0"/>
-        <v>-0.94000000000000039</v>
-      </c>
-      <c r="G14" s="9">
-        <v>0.64930555555555558</v>
-      </c>
-      <c r="H14" s="9">
-        <v>0.19236111111111112</v>
-      </c>
-      <c r="I14" s="20">
-        <v>62.09</v>
+        <v>-1.0899999999999999</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0.69166666666666676</v>
+      </c>
+      <c r="I14" s="16">
+        <v>75.25</v>
       </c>
       <c r="J14" s="7">
-        <v>1.355</v>
+        <v>1.3480000000000001</v>
       </c>
       <c r="K14" s="7">
-        <v>26.59</v>
+        <v>33.42</v>
       </c>
       <c r="L14" s="7">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M14" s="7">
         <f t="shared" si="1"/>
-        <v>-5.6936118462499498E-4</v>
+        <v>-1.0745585930183264E-2</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="6"/>
+      <c r="C15" s="7"/>
       <c r="D15" s="7">
-        <v>7.66</v>
+        <v>7.72</v>
       </c>
       <c r="E15" s="7">
-        <v>6.57</v>
+        <v>7.33</v>
       </c>
       <c r="F15" s="7">
         <f t="shared" si="0"/>
-        <v>-1.0899999999999999</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>21</v>
+        <v>-0.38999999999999968</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0.64166666666666672</v>
       </c>
       <c r="H15" s="8">
-        <v>0.69166666666666676</v>
-      </c>
-      <c r="I15" s="20">
-        <v>75.25</v>
+        <v>0.68819444444444444</v>
+      </c>
+      <c r="I15" s="16">
+        <v>67</v>
       </c>
       <c r="J15" s="7">
-        <v>1.3480000000000001</v>
+        <v>1.35</v>
       </c>
       <c r="K15" s="7">
-        <v>33.42</v>
+        <v>27.54</v>
       </c>
       <c r="L15" s="7">
         <v>80</v>
       </c>
       <c r="M15" s="7">
         <f t="shared" si="1"/>
-        <v>-4.3342459107980372E-4</v>
+        <v>-4.3117744610281887E-3</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7">
-        <v>7.72</v>
+        <v>7.04</v>
       </c>
       <c r="E16" s="7">
-        <v>7.33</v>
+        <v>6.37</v>
       </c>
       <c r="F16" s="7">
         <f t="shared" si="0"/>
-        <v>-0.38999999999999968</v>
-      </c>
-      <c r="G16" s="8">
-        <v>0.64166666666666672</v>
-      </c>
-      <c r="H16" s="8">
-        <v>0.68819444444444444</v>
-      </c>
-      <c r="I16" s="20">
-        <v>67</v>
+        <v>-0.66999999999999993</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="16">
+        <v>45</v>
       </c>
       <c r="J16" s="7">
-        <v>1.35</v>
+        <v>1.395</v>
       </c>
       <c r="K16" s="7">
-        <v>27.54</v>
+        <v>21.92</v>
       </c>
       <c r="L16" s="7">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="M16" s="7">
         <f t="shared" si="1"/>
-        <v>-2.1136149318765632E-4</v>
+        <v>-1.0673038630027876E-2</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7">
-        <v>7.04</v>
+        <v>7.77</v>
       </c>
       <c r="E17" s="7">
-        <v>6.37</v>
+        <v>7.13</v>
       </c>
       <c r="F17" s="7">
         <f t="shared" si="0"/>
-        <v>-0.66999999999999993</v>
+        <v>-0.63999999999999968</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H17" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="I17" s="20">
-        <v>45</v>
+      <c r="I17" s="16">
+        <v>90</v>
       </c>
       <c r="J17" s="7">
-        <v>1.395</v>
+        <v>1.4</v>
       </c>
       <c r="K17" s="7">
-        <v>21.92</v>
+        <v>28.96</v>
       </c>
       <c r="L17" s="7">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M17" s="7">
         <f t="shared" si="1"/>
-        <v>-6.7923763179237619E-4</v>
+        <v>-5.0793650793650776E-3</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7">
-        <v>7.77</v>
+        <v>7.34</v>
       </c>
       <c r="E18" s="7">
-        <v>7.13</v>
+        <v>6.66</v>
       </c>
       <c r="F18" s="7">
         <f t="shared" si="0"/>
-        <v>-0.63999999999999968</v>
+        <v>-0.67999999999999972</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="20">
-        <v>90</v>
+        <v>35</v>
+      </c>
+      <c r="I18" s="16">
+        <v>60</v>
       </c>
       <c r="J18" s="7">
-        <v>1.4</v>
+        <v>1.379</v>
       </c>
       <c r="K18" s="7">
-        <v>28.96</v>
+        <v>28.75</v>
       </c>
       <c r="L18" s="7">
-        <v>68</v>
+        <v>75.5</v>
       </c>
       <c r="M18" s="7">
         <f t="shared" si="1"/>
-        <v>-2.4554941682013496E-4</v>
+        <v>-8.2185158327290272E-3</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="7"/>
+        <v>13</v>
+      </c>
+      <c r="C19" s="6"/>
       <c r="D19" s="7">
-        <v>7.34</v>
+        <v>7.64</v>
       </c>
       <c r="E19" s="7">
-        <v>6.66</v>
+        <v>6.96</v>
       </c>
       <c r="F19" s="7">
         <f t="shared" si="0"/>
         <v>-0.67999999999999972</v>
       </c>
-      <c r="G19" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I19" s="20">
+      <c r="G19" s="8">
+        <v>0.63888888888888895</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0.69305555555555554</v>
+      </c>
+      <c r="I19" s="16">
+        <v>78.58</v>
+      </c>
+      <c r="J19" s="7">
+        <v>1.39</v>
+      </c>
+      <c r="K19" s="7">
+        <v>15.33</v>
+      </c>
+      <c r="L19" s="7">
         <v>60</v>
       </c>
-      <c r="J19" s="7">
-        <v>1.379</v>
-      </c>
-      <c r="K19" s="7">
-        <v>28.75</v>
-      </c>
-      <c r="L19" s="7">
-        <v>75.5</v>
-      </c>
       <c r="M19" s="7">
         <f t="shared" si="1"/>
-        <v>-3.9420289855072446E-4</v>
+        <v>-6.2256125361863706E-3</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="7">
-        <v>7.64</v>
+        <v>7.8</v>
       </c>
       <c r="E20" s="7">
-        <v>6.96</v>
+        <v>6.39</v>
       </c>
       <c r="F20" s="7">
         <f t="shared" si="0"/>
-        <v>-0.67999999999999972</v>
-      </c>
-      <c r="G20" s="8">
-        <v>0.63888888888888895</v>
-      </c>
-      <c r="H20" s="8">
-        <v>0.69305555555555554</v>
-      </c>
-      <c r="I20" s="20">
-        <v>78.58</v>
+        <v>-1.4100000000000001</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="16">
+        <v>100</v>
       </c>
       <c r="J20" s="7">
-        <v>1.39</v>
+        <v>1.4079999999999999</v>
       </c>
       <c r="K20" s="7">
-        <v>15.33</v>
+        <v>17.63</v>
       </c>
       <c r="L20" s="7">
         <v>60</v>
       </c>
       <c r="M20" s="7">
         <f t="shared" si="1"/>
-        <v>-5.6448802513366309E-4</v>
+        <v>-1.0014204545454547E-2</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="7">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="E21" s="7">
-        <v>6.39</v>
+        <v>6.85</v>
       </c>
       <c r="F21" s="7">
         <f t="shared" si="0"/>
-        <v>-1.4100000000000001</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>22</v>
+        <v>-1.25</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>19</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I21" s="20">
-        <v>100</v>
+        <v>20</v>
+      </c>
+      <c r="I21" s="16">
+        <v>80</v>
       </c>
       <c r="J21" s="7">
-        <v>1.4079999999999999</v>
+        <v>1.4850000000000001</v>
       </c>
       <c r="K21" s="7">
-        <v>17.63</v>
+        <v>23.2</v>
       </c>
       <c r="L21" s="7">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M21" s="7">
         <f t="shared" si="1"/>
-        <v>-7.9977311401020995E-4</v>
+        <v>-1.0521885521885521E-2</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="6"/>
+      <c r="C22" s="7"/>
       <c r="D22" s="7">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="E22" s="7">
-        <v>6.85</v>
+        <v>6.02</v>
       </c>
       <c r="F22" s="7">
         <f t="shared" si="0"/>
-        <v>-1.25</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I22" s="20">
-        <v>80</v>
+        <v>-1.1800000000000006</v>
+      </c>
+      <c r="G22" s="8">
+        <v>0.63472222222222219</v>
+      </c>
+      <c r="H22" s="8">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="I22" s="16">
+        <v>61</v>
       </c>
       <c r="J22" s="7">
-        <v>1.4850000000000001</v>
+        <v>1.335</v>
       </c>
       <c r="K22" s="7">
-        <v>23.2</v>
+        <v>32.659999999999997</v>
       </c>
       <c r="L22" s="7">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="M22" s="7">
         <f t="shared" si="1"/>
-        <v>-6.7349137931034487E-4</v>
+        <v>-1.4490084116166275E-2</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7">
-        <v>7.2</v>
+        <v>7.56</v>
       </c>
       <c r="E23" s="7">
-        <v>6.02</v>
+        <v>7</v>
       </c>
       <c r="F23" s="7">
         <f t="shared" si="0"/>
-        <v>-1.1800000000000006</v>
-      </c>
-      <c r="G23" s="8">
-        <v>0.63472222222222219</v>
+        <v>-0.55999999999999961</v>
+      </c>
+      <c r="G23" s="9">
+        <v>0.14444444444444446</v>
       </c>
       <c r="H23" s="8">
-        <v>0.67708333333333337</v>
-      </c>
-      <c r="I23" s="20">
-        <v>61</v>
+        <v>0.19444444444444445</v>
+      </c>
+      <c r="I23" s="16">
+        <v>60.5</v>
       </c>
       <c r="J23" s="7">
-        <v>1.335</v>
+        <v>1.395</v>
       </c>
       <c r="K23" s="7">
-        <v>32.659999999999997</v>
+        <v>16.02</v>
       </c>
       <c r="L23" s="7">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="M23" s="7">
         <f t="shared" si="1"/>
-        <v>-5.9229217070061175E-4</v>
+        <v>-6.635267632335076E-3</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7">
-        <v>7.56</v>
+        <v>7.53</v>
       </c>
       <c r="E24" s="7">
-        <v>7</v>
+        <v>6.39</v>
       </c>
       <c r="F24" s="7">
         <f t="shared" si="0"/>
-        <v>-0.55999999999999961</v>
-      </c>
-      <c r="G24" s="9">
-        <v>0.14444444444444446</v>
+        <v>-1.1400000000000006</v>
+      </c>
+      <c r="G24" s="10">
+        <v>0.63611111111111118</v>
       </c>
       <c r="H24" s="8">
-        <v>0.19444444444444445</v>
-      </c>
-      <c r="I24" s="20">
-        <v>60.5</v>
+        <v>0.67847222222222225</v>
+      </c>
+      <c r="I24" s="16">
+        <v>61</v>
       </c>
       <c r="J24" s="7">
-        <v>1.395</v>
+        <v>1.385</v>
       </c>
       <c r="K24" s="7">
-        <v>16.02</v>
+        <v>35.479999999999997</v>
       </c>
       <c r="L24" s="7">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="M24" s="7">
         <f t="shared" si="1"/>
-        <v>-5.7779015899547012E-4</v>
+        <v>-1.3493519559685158E-2</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7">
-        <v>7.53</v>
+        <v>7.56</v>
       </c>
       <c r="E25" s="7">
-        <v>6.39</v>
+        <v>6.82</v>
       </c>
       <c r="F25" s="7">
         <f t="shared" si="0"/>
-        <v>-1.1400000000000006</v>
-      </c>
-      <c r="G25" s="10">
-        <v>0.63611111111111118</v>
-      </c>
-      <c r="H25" s="8">
-        <v>0.67847222222222225</v>
-      </c>
-      <c r="I25" s="20">
-        <v>61</v>
+        <v>-0.73999999999999932</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I25" s="16">
+        <v>78</v>
       </c>
       <c r="J25" s="7">
-        <v>1.385</v>
+        <v>1.458</v>
       </c>
       <c r="K25" s="7">
-        <v>35.479999999999997</v>
+        <v>22.6</v>
       </c>
       <c r="L25" s="7">
         <v>68</v>
       </c>
       <c r="M25" s="7">
         <f t="shared" si="1"/>
-        <v>-5.2673406398432766E-4</v>
+        <v>-6.5069818156237857E-3</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7">
-        <v>7.56</v>
+        <v>7.88</v>
       </c>
       <c r="E26" s="7">
-        <v>6.82</v>
+        <v>7.09</v>
       </c>
       <c r="F26" s="7">
         <f t="shared" si="0"/>
-        <v>-0.73999999999999932</v>
+        <v>-0.79</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="I26" s="20">
-        <v>78</v>
+        <v>38</v>
+      </c>
+      <c r="I26" s="16">
+        <v>76</v>
       </c>
       <c r="J26" s="7">
-        <v>1.458</v>
+        <v>1.3779999999999999</v>
       </c>
       <c r="K26" s="7">
-        <v>22.6</v>
+        <v>21.57</v>
       </c>
       <c r="L26" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M26" s="7">
         <f t="shared" si="1"/>
-        <v>-4.197867029725433E-4</v>
+        <v>-7.5433503934000468E-3</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7">
-        <v>7.88</v>
+        <v>7.29</v>
       </c>
       <c r="E27" s="7">
-        <v>7.09</v>
+        <v>6.29</v>
       </c>
       <c r="F27" s="7">
         <f t="shared" si="0"/>
-        <v>-0.79</v>
+        <v>-1</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="I27" s="20">
-        <v>76</v>
+        <v>32</v>
+      </c>
+      <c r="I27" s="16">
+        <v>60</v>
       </c>
       <c r="J27" s="7">
-        <v>1.3779999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="K27" s="7">
-        <v>21.57</v>
+        <v>27.27</v>
       </c>
       <c r="L27" s="7">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="M27" s="7">
         <f t="shared" si="1"/>
-        <v>-4.8190713222555695E-4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" s="6">
-        <v>23</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7">
-        <v>7.29</v>
-      </c>
-      <c r="E28" s="7">
-        <v>6.29</v>
-      </c>
-      <c r="F28" s="7">
-        <f t="shared" si="0"/>
-        <v>-1</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="20">
-        <v>60</v>
-      </c>
-      <c r="J28" s="7">
-        <v>1.44</v>
-      </c>
-      <c r="K28" s="7">
-        <v>27.27</v>
-      </c>
-      <c r="L28" s="7">
-        <v>66</v>
-      </c>
-      <c r="M28" s="7">
-        <f t="shared" si="1"/>
-        <v>-6.1117222833394452E-4</v>
+        <v>-1.1574074074074075E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1761,7 +2920,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1827,15 +2986,15 @@
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="14"/>
-      <c r="F4" s="15" t="s">
+      <c r="E4" s="17"/>
+      <c r="F4" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="17"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="20"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
